--- a/artfynd/A 12413-2023 artfynd.xlsx
+++ b/artfynd/A 12413-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 12413-2023 artfynd.xlsx
+++ b/artfynd/A 12413-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,48 +675,37 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>93683541</v>
+        <v>93683594</v>
       </c>
       <c r="B2" t="n">
-        <v>5113</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>81312</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100526</v>
+        <v>1049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -724,13 +713,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>352560.0287182664</v>
+        <v>352573</v>
       </c>
       <c r="R2" t="n">
-        <v>6536661.298731959</v>
+        <v>6536690</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -757,24 +746,14 @@
           <t>2021-05-22</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2021-05-22</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Kläckhål i flera granar i närområdet</t>
+          <t>I murken tallshögstubbe i myrkant/sumpskog</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -799,6 +778,118 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>93683541</v>
+      </c>
+      <c r="B3" t="n">
+        <v>5179</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Sumpskog NO Stora Olevattnet, Dls</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>352560</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6536661</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Åmål</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Fröskog</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2021-05-22</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2021-05-22</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Kläckhål i flera granar i närområdet</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Roger Gran</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Roger Gran</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
